--- a/data/GPS/Metricas_GPS.xlsx
+++ b/data/GPS/Metricas_GPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30405"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\ADARVE JUV D.H\App_Rendimiento_Futbol\data\GPS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE5929F-8C05-488E-8840-B54F7164F3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{2CE5929F-8C05-488E-8840-B54F7164F3D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2F8E425D-C9DA-4486-A50E-D430977FDCA0}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t>Fecha</t>
   </si>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>Defensa Central</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alejandro_Garcia_Gumiel </t>
   </si>
   <si>
     <t xml:space="preserve">Noah_Ojo_Barranco </t>
@@ -434,7 +431,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="7" width="22.21875" customWidth="1"/>
@@ -691,40 +688,40 @@
         <v>26</v>
       </c>
       <c r="D6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="1">
+        <v>4.0890000000000004</v>
+      </c>
+      <c r="F6" s="1">
+        <v>5.8999999999999997E-2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>0</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1">
         <v>25</v>
       </c>
-      <c r="E6" s="1">
-        <v>3.7959999999999998</v>
-      </c>
-      <c r="F6" s="1">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="G6" s="1">
-        <v>0</v>
-      </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>17</v>
-      </c>
       <c r="K6" s="1">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="L6" s="1">
-        <v>4.0250000000000004</v>
+        <v>4.3540000000000001</v>
       </c>
       <c r="M6" s="1">
-        <v>-4.53</v>
+        <v>-5.3540000000000001</v>
       </c>
       <c r="N6" s="1">
-        <v>20.34</v>
+        <v>22.806000000000001</v>
       </c>
       <c r="O6" s="1">
-        <v>903.4</v>
+        <v>1045.5</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -735,16 +732,16 @@
         <v>71.62</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E7" s="1">
-        <v>4.0890000000000004</v>
+        <v>4.1870000000000003</v>
       </c>
       <c r="F7" s="1">
-        <v>5.8999999999999997E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="G7" s="1">
         <v>0</v>
@@ -756,22 +753,22 @@
         <v>0</v>
       </c>
       <c r="J7" s="1">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="K7" s="1">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L7" s="1">
-        <v>4.3540000000000001</v>
+        <v>4.6289999999999996</v>
       </c>
       <c r="M7" s="1">
-        <v>-5.3540000000000001</v>
+        <v>-4.931</v>
       </c>
       <c r="N7" s="1">
-        <v>22.806000000000001</v>
+        <v>24.196000000000002</v>
       </c>
       <c r="O7" s="1">
-        <v>1045.5</v>
+        <v>1287.2</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -788,10 +785,10 @@
         <v>22</v>
       </c>
       <c r="E8" s="1">
-        <v>4.1870000000000003</v>
+        <v>2.6389999999999998</v>
       </c>
       <c r="F8" s="1">
-        <v>4.2999999999999997E-2</v>
+        <v>0.03</v>
       </c>
       <c r="G8" s="1">
         <v>0</v>
@@ -803,22 +800,22 @@
         <v>0</v>
       </c>
       <c r="J8" s="1">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="K8" s="1">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="L8" s="1">
-        <v>4.6289999999999996</v>
+        <v>4.57</v>
       </c>
       <c r="M8" s="1">
-        <v>-4.931</v>
+        <v>-3.6909999999999998</v>
       </c>
       <c r="N8" s="1">
-        <v>24.196000000000002</v>
+        <v>20.861999999999998</v>
       </c>
       <c r="O8" s="1">
-        <v>1287.2</v>
+        <v>506.2</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
@@ -832,13 +829,13 @@
         <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="E9" s="1">
-        <v>2.6389999999999998</v>
+        <v>4.5309999999999997</v>
       </c>
       <c r="F9" s="1">
-        <v>0.03</v>
+        <v>7.8E-2</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
@@ -850,22 +847,22 @@
         <v>0</v>
       </c>
       <c r="J9" s="1">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="K9" s="1">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="L9" s="1">
-        <v>4.57</v>
+        <v>4.62</v>
       </c>
       <c r="M9" s="1">
-        <v>-3.6909999999999998</v>
+        <v>-5.0359999999999996</v>
       </c>
       <c r="N9" s="1">
-        <v>20.861999999999998</v>
+        <v>23.53</v>
       </c>
       <c r="O9" s="1">
-        <v>506.2</v>
+        <v>1226.8</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
@@ -879,13 +876,13 @@
         <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="E10" s="1">
-        <v>4.5309999999999997</v>
+        <v>4.1660000000000004</v>
       </c>
       <c r="F10" s="1">
-        <v>7.8E-2</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="G10" s="1">
         <v>0</v>
@@ -897,22 +894,22 @@
         <v>0</v>
       </c>
       <c r="J10" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K10" s="1">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="L10" s="1">
-        <v>4.62</v>
+        <v>4.4290000000000003</v>
       </c>
       <c r="M10" s="1">
-        <v>-5.0359999999999996</v>
+        <v>-4.726</v>
       </c>
       <c r="N10" s="1">
-        <v>23.53</v>
+        <v>25.067</v>
       </c>
       <c r="O10" s="1">
-        <v>1226.8</v>
+        <v>1102.2</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -923,16 +920,16 @@
         <v>71.62</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="E11" s="1">
-        <v>4.1660000000000004</v>
+        <v>3.919</v>
       </c>
       <c r="F11" s="1">
-        <v>8.4000000000000005E-2</v>
+        <v>7.2999999999999995E-2</v>
       </c>
       <c r="G11" s="1">
         <v>0</v>
@@ -944,22 +941,22 @@
         <v>0</v>
       </c>
       <c r="J11" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K11" s="1">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="L11" s="1">
-        <v>4.4290000000000003</v>
+        <v>3.6440000000000001</v>
       </c>
       <c r="M11" s="1">
-        <v>-4.726</v>
+        <v>-4.7409999999999997</v>
       </c>
       <c r="N11" s="1">
-        <v>25.067</v>
+        <v>23.766999999999999</v>
       </c>
       <c r="O11" s="1">
-        <v>1102.2</v>
+        <v>825.1</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -973,13 +970,13 @@
         <v>34</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E12" s="1">
-        <v>3.919</v>
+        <v>3.887</v>
       </c>
       <c r="F12" s="1">
-        <v>7.2999999999999995E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
@@ -991,68 +988,21 @@
         <v>0</v>
       </c>
       <c r="J12" s="1">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="K12" s="1">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="L12" s="1">
-        <v>3.6440000000000001</v>
+        <v>4.2320000000000002</v>
       </c>
       <c r="M12" s="1">
-        <v>-4.7409999999999997</v>
+        <v>-5.7839999999999998</v>
       </c>
       <c r="N12" s="1">
-        <v>23.766999999999999</v>
+        <v>24.041</v>
       </c>
       <c r="O12" s="1">
-        <v>825.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
-        <v>46237</v>
-      </c>
-      <c r="B13" s="1">
-        <v>71.62</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="1">
-        <v>3.887</v>
-      </c>
-      <c r="F13" s="1">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="G13" s="1">
-        <v>0</v>
-      </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
-        <v>35</v>
-      </c>
-      <c r="K13" s="1">
-        <v>17</v>
-      </c>
-      <c r="L13" s="1">
-        <v>4.2320000000000002</v>
-      </c>
-      <c r="M13" s="1">
-        <v>-5.7839999999999998</v>
-      </c>
-      <c r="N13" s="1">
-        <v>24.041</v>
-      </c>
-      <c r="O13" s="1">
         <v>972.5</v>
       </c>
     </row>
